--- a/python-in-excel-two-way-lookup.xlsx
+++ b/python-in-excel-two-way-lookup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AC6925B-57D6-4AB3-9283-0FEB066D1C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA0CA5E-2888-4F56-9862-5FC497BDFB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{BC68B47E-19F2-41FC-8E73-73B52794998F}"/>
   </bookViews>
@@ -36,6 +36,63 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
+<python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
+  <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
+    <initialization>
+      <code xml:space="preserve">import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+import seaborn as sns
+import statsmodels as sm
+import excel
+import warnings
+warnings.simplefilter('ignore')
+excel.set_xl_scalar_conversion(excel.convert_to_scalar)
+excel.set_xl_array_conversion(excel.convert_to_dataframe)
+</code>
+    </initialization>
+  </environmentDefinition>
+  <pythonScripts>
+    <pythonScript>
+      <code>movies_df = xl(%P2%, headers=True)
+movies_df = movies_df.set_index('Movie')</code>
+    </pythonScript>
+    <pythonScript>
+      <code>movies_df.loc['Casablanca', 'Reviews']</code>
+    </pythonScript>
+    <pythonScript>
+      <code>movies_df.loc['Casablanca', ['Year', 'Rating']]</code>
+    </pythonScript>
+    <pythonScript>
+      <code>movies_df.loc[['Casablanca', 'The Kid'], ['Year', 'Rating']]</code>
+    </pythonScript>
+  </pythonScripts>
+</python>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -120,12 +177,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -135,43 +191,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -247,6 +266,43 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -261,13 +317,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C86E102C-1449-4F90-8B3D-FC0A64397E52}" name="Table1" displayName="Table1" ref="A1:D6" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C86E102C-1449-4F90-8B3D-FC0A64397E52}" name="movies" displayName="movies" ref="A1:D6" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A1:D6" xr:uid="{C86E102C-1449-4F90-8B3D-FC0A64397E52}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{93C47F8F-5241-44DD-8ABA-D8AD7929241C}" name="Movie" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{BD879CB6-1B54-4885-9444-4C4E9399B51C}" name="Year" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{D3E62A7D-D54A-461B-9073-8C600EBA2AB7}" name="Reviews" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{BAC2EA53-F9C3-434D-BF51-22ED712B8B0A}" name="Rating" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{93C47F8F-5241-44DD-8ABA-D8AD7929241C}" name="Movie" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{BD879CB6-1B54-4885-9444-4C4E9399B51C}" name="Year" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{D3E62A7D-D54A-461B-9073-8C600EBA2AB7}" name="Reviews" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{BAC2EA53-F9C3-434D-BF51-22ED712B8B0A}" name="Rating" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -590,93 +646,269 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E83E01B-3163-4F02-BF04-459ED96DD031}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="1" max="1" width="11.8125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.85">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.85">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>1941</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>116</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>0.99</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>1942</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>122</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>0.99</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>1939</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>121</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>0.98</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>1936</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>61</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1921</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>44</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A8" t="str" cm="1">
+        <f t="array" ref="A8:D14">_xlfn._xlws.PY(0,0,movies[#All])</f>
+        <v/>
+      </c>
+      <c r="B8" t="str">
+        <v>Year</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Reviews</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Rating</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A9" t="str">
+        <v>Movie</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A10" t="str">
+        <v>Citizen Kane</v>
+      </c>
+      <c r="B10">
+        <v>1941</v>
+      </c>
+      <c r="C10">
+        <v>116</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A11" t="str">
+        <v>Casablanca</v>
+      </c>
+      <c r="B11">
+        <v>1942</v>
+      </c>
+      <c r="C11">
+        <v>122</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A12" t="str">
+        <v>Wizard of Oz</v>
+      </c>
+      <c r="B12">
+        <v>1939</v>
+      </c>
+      <c r="C12">
+        <v>121</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A13" t="str">
+        <v>Modern Times</v>
+      </c>
+      <c r="B13">
+        <v>1936</v>
+      </c>
+      <c r="C13">
+        <v>61</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A14" t="str">
+        <v>The Kid</v>
+      </c>
+      <c r="B14">
+        <v>1921</v>
+      </c>
+      <c r="C14">
+        <v>44</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A16" cm="1">
+        <f t="array" ref="A16">_xlfn._xlws.PY(1,0)</f>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A18" t="str" cm="1">
+        <f t="array" ref="A18:B20">_xlfn._xlws.PY(2,0)</f>
+        <v/>
+      </c>
+      <c r="B18" t="str">
+        <v>Casablanca</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A19" t="str">
+        <v>Year</v>
+      </c>
+      <c r="B19">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A20" t="str">
+        <v>Rating</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A22" t="str" cm="1">
+        <f t="array" ref="A22:C25">_xlfn._xlws.PY(3,0)</f>
+        <v/>
+      </c>
+      <c r="B22" t="str">
+        <v>Year</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Rating</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A23" t="str">
+        <v>Movie</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A24" t="str">
+        <v>Casablanca</v>
+      </c>
+      <c r="B24">
+        <v>1942</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A25" t="str">
+        <v>The Kid</v>
+      </c>
+      <c r="B25">
+        <v>1921</v>
+      </c>
+      <c r="C25" s="3">
         <v>1</v>
       </c>
     </row>

--- a/python-in-excel-two-way-lookup.xlsx
+++ b/python-in-excel-two-way-lookup.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA0CA5E-2888-4F56-9862-5FC497BDFB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A520A86-DE84-4528-B466-999ACFAFAFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{BC68B47E-19F2-41FC-8E73-73B52794998F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="lookups" sheetId="1" r:id="rId1"/>
+    <sheet name="helper" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -63,7 +64,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -91,12 +92,32 @@
     <pythonScript>
       <code>movies_df.loc[['Casablanca', 'The Kid'], ['Year', 'Rating']]</code>
     </pythonScript>
+    <pythonScript>
+      <code>movies_df.index</code>
+    </pythonScript>
+    <pythonScript>
+      <code>movies_df.columns</code>
+    </pythonScript>
+    <pythonScript>
+      <code>def force_to_list(value):
+    if isinstance(value, pd.DataFrame):
+        return value.values.flatten().tolist()
+    elif isinstance(value, str):
+        return [value]  # Wrap single string in a list
+    elif hasattr(value, '__iter__') and not isinstance(value, str):
+        return list(value)  # Handle other iterable types
+    else:
+        return [value]  # Wrap scalars in a list
+#movies_df.loc[['Casablanca', 'The Kid'], ['Year', 'Rating']]  
+movies_df.loc[force_to_list(xl(%P2%)),
+              force_to_list(xl(%P3%))]</code>
+    </pythonScript>
   </pythonScripts>
 </python>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Movie</t>
   </si>
@@ -123,6 +144,12 @@
   </si>
   <si>
     <t>The Kid</t>
+  </si>
+  <si>
+    <t>Choose metrics:</t>
+  </si>
+  <si>
+    <t>Choose movies:</t>
   </si>
 </sst>
 </file>
@@ -177,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -186,6 +213,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -314,6 +350,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -646,11 +699,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E83E01B-3163-4F02-BF04-459ED96DD031}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
   <cols>
-    <col min="1" max="1" width="11.8125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.73828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.8125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.8125" customWidth="1"/>
+    <col min="9" max="9" width="8.73828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.85">
@@ -842,7 +899,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.85">
       <c r="A18" t="str" cm="1">
         <f t="array" ref="A18:B20">_xlfn._xlws.PY(2,0)</f>
         <v/>
@@ -851,7 +908,7 @@
         <v>Casablanca</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.85">
       <c r="A19" t="str">
         <v>Year</v>
       </c>
@@ -859,7 +916,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.85">
       <c r="A20" t="str">
         <v>Rating</v>
       </c>
@@ -867,7 +924,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.85">
       <c r="A22" t="str" cm="1">
         <f t="array" ref="A22:C25">_xlfn._xlws.PY(3,0)</f>
         <v/>
@@ -879,7 +936,7 @@
         <v>Rating</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.85">
       <c r="A23" t="str">
         <v>Movie</v>
       </c>
@@ -890,7 +947,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.85">
       <c r="A24" t="str">
         <v>Casablanca</v>
       </c>
@@ -901,7 +958,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.85">
       <c r="A25" t="str">
         <v>The Kid</v>
       </c>
@@ -912,10 +969,213 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.85">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.85">
+      <c r="A28" t="str" cm="1">
+        <f t="array" ref="A28:A32">_xlfn._xlws.PY(4,0)</f>
+        <v>Citizen Kane</v>
+      </c>
+      <c r="B28" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" t="str" cm="1">
+        <f t="array" ref="D28:D30">_xlfn._xlws.PY(5,0)</f>
+        <v>Year</v>
+      </c>
+      <c r="E28" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.85">
+      <c r="A29" t="str">
+        <v>Casablanca</v>
+      </c>
+      <c r="B29" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Reviews</v>
+      </c>
+      <c r="E29" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.85">
+      <c r="A30" t="str">
+        <v>Wizard of Oz</v>
+      </c>
+      <c r="B30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Rating</v>
+      </c>
+      <c r="E30" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.85">
+      <c r="A31" t="str">
+        <v>Modern Times</v>
+      </c>
+      <c r="B31" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.85">
+      <c r="A32" t="str">
+        <v>The Kid</v>
+      </c>
+      <c r="B32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A34" t="str" cm="1">
+        <f t="array" aca="1" ref="A34:D38" ca="1">_xlfn._xlws.PY(6,0,_xlfn.ANCHORARRAY(helper!A1),_xlfn.ANCHORARRAY(helper!C1))</f>
+        <v/>
+      </c>
+      <c r="B34" t="str">
+        <f ca="1"/>
+        <v>Year</v>
+      </c>
+      <c r="C34" t="str">
+        <f ca="1"/>
+        <v>Reviews</v>
+      </c>
+      <c r="D34" s="7" t="str">
+        <f ca="1"/>
+        <v>Rating</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A35" t="str">
+        <f ca="1"/>
+        <v>Movie</v>
+      </c>
+      <c r="B35" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="D35" s="8" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A36" t="str">
+        <f ca="1"/>
+        <v>Citizen Kane</v>
+      </c>
+      <c r="B36">
+        <f ca="1"/>
+        <v>1941</v>
+      </c>
+      <c r="C36">
+        <f ca="1"/>
+        <v>116</v>
+      </c>
+      <c r="D36" s="8">
+        <f ca="1"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A37" t="str">
+        <f ca="1"/>
+        <v>Casablanca</v>
+      </c>
+      <c r="B37">
+        <f ca="1"/>
+        <v>1942</v>
+      </c>
+      <c r="C37">
+        <f ca="1"/>
+        <v>122</v>
+      </c>
+      <c r="D37" s="8">
+        <f ca="1"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A38" t="str">
+        <f ca="1"/>
+        <v>Wizard of Oz</v>
+      </c>
+      <c r="B38">
+        <f ca="1"/>
+        <v>1939</v>
+      </c>
+      <c r="C38">
+        <f ca="1"/>
+        <v>121</v>
+      </c>
+      <c r="D38" s="8">
+        <f ca="1"/>
+        <v>0.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A4F633-203C-4328-BA08-0372D60685C7}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1:A3" ca="1">_xlfn._xlws.FILTER(_xlfn.ANCHORARRAY(lookups!A28), OFFSET(_xlfn.ANCHORARRAY(lookups!A28), , 1) = TRUE)</f>
+        <v>Citizen Kane</v>
+      </c>
+      <c r="C1" t="str" cm="1">
+        <f t="array" aca="1" ref="C1:C3" ca="1">_xlfn._xlws.FILTER(_xlfn.ANCHORARRAY(lookups!D28), OFFSET(_xlfn.ANCHORARRAY(lookups!D28), , 1) = TRUE)</f>
+        <v>Year</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A2" t="str">
+        <f ca="1"/>
+        <v>Casablanca</v>
+      </c>
+      <c r="C2" t="str">
+        <f ca="1"/>
+        <v>Reviews</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A3" t="str">
+        <f ca="1"/>
+        <v>Wizard of Oz</v>
+      </c>
+      <c r="C3" t="str">
+        <f ca="1"/>
+        <v>Rating</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>